--- a/forms/trg/Formulir_TRG_lcpr-rg.xlsx
+++ b/forms/trg/Formulir_TRG_lcpr-rg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B24)</f>
+        <f>COUNTA(Anggota!B5:B25)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F24)</f>
+        <f>COUNTA(Anggota!F5:F25)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,12 +913,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Haeranah, S.H., M.H</t>
+          <t>Prof. Dr. Syamsuddin Muchtar, S.H., M.H</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -928,20 +928,20 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Criminal Law</t>
+          <t>Criminal Law, Child Protection</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>0009-0001-0742-6966</t>
-        </is>
-      </c>
+      <c r="J5" s="12" t="n"/>
       <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>57194418367</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -954,12 +954,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. Nur Azisa, S.H., M.H</t>
+          <t>Dr. Haeranah, S.H., M.H</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -978,15 +978,11 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0009-0005-0391-2237</t>
+          <t>0009-0001-0742-6966</t>
         </is>
       </c>
       <c r="K6" s="12" t="n"/>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>57207767458</t>
-        </is>
-      </c>
+      <c r="L6" s="12" t="n"/>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -999,12 +995,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Audyna Mayasari, S.H., M.H., M.M., CLA</t>
+          <t>Dr. Nur Azisa, S.H., M.H</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1014,16 +1010,24 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Criminal Law, Social Science</t>
+          <t>Criminal Law</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="12" t="n"/>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>0009-0005-0391-2237</t>
+        </is>
+      </c>
       <c r="K7" s="12" t="n"/>
-      <c r="L7" s="12" t="n"/>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>57207767458</t>
+        </is>
+      </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1036,12 +1040,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>M. Aris Munandar, S.H., M.H</t>
+          <t>Dr. Audyna Mayasari, S.H., M.H., M.M., CLA</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1051,24 +1055,16 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Criminal Law, Health Law</t>
+          <t>Criminal Law, Social Science</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>0009-0007-2833-5936</t>
-        </is>
-      </c>
+      <c r="J8" s="12" t="n"/>
       <c r="K8" s="12" t="n"/>
-      <c r="L8" s="11" t="inlineStr">
-        <is>
-          <t>58785428300</t>
-        </is>
-      </c>
+      <c r="L8" s="12" t="n"/>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1081,12 +1077,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Afif Muhni, S.H., M.H</t>
+          <t>M. Aris Munandar, S.H., M.H</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1096,7 +1092,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Criminal Law, Banking Crime, Money Laundering, Asset Recovery</t>
+          <t>Criminal Law, Health Law</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1105,11 +1101,15 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0009-0003-7716-4425</t>
+          <t>0009-0007-2833-5936</t>
         </is>
       </c>
       <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>58785428300</t>
+        </is>
+      </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1122,22 +1122,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr. Nurul Hidayat Ab Rahman</t>
+          <t>Afif Muhni, S.H., M.H</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Universiti Kebangsaan Malaysia (UKM)</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Child Law, Sustainable Development Goals, Sustainable Development, Family Law, Islamic Family Law</t>
+          <t>Criminal Law, Banking Crime, Money Laundering, Asset Recovery</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1146,7 +1146,7 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-1008-4263</t>
+          <t>0009-0003-7716-4425</t>
         </is>
       </c>
       <c r="K10" s="12" t="n"/>
@@ -1163,29 +1163,33 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Ulfadrian Mandalani, S.H., M.H</t>
+          <t>Dr. Nurul Hidayat Ab Rahman</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Instansi xxxxx</t>
+          <t>Universiti Kebangsaan Malaysia (UKM)</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>(Doctoral/Magister/GRaduate)</t>
+          <t>Child Law, Sustainable Development Goals, Sustainable Development, Family Law, Islamic Family Law</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
-      <c r="J11" s="12" t="n"/>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-1008-4263</t>
+        </is>
+      </c>
       <c r="K11" s="12" t="n"/>
       <c r="L11" s="12" t="n"/>
       <c r="M11" s="11" t="inlineStr">
@@ -1200,22 +1204,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Dedy Meidixon</t>
+          <t>Ulfadrian Mandalani, S.H., M.H</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Law</t>
+          <t>Instansi xxxxx</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>LCPR – Team</t>
+          <t>(Doctoral/Magister/GRaduate)</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1235,10 +1239,26 @@
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="11" t="n"/>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Dedy Meidixon</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Law</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>LCPR – Team</t>
+        </is>
+      </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
@@ -1246,7 +1266,11 @@
       <c r="J13" s="12" t="n"/>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="12" t="n"/>
-      <c r="M13" s="12" t="n"/>
+      <c r="M13" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1435,15 +1459,32 @@
       <c r="L24" s="12" t="n"/>
       <c r="M24" s="12" t="n"/>
     </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="12" t="n"/>
+      <c r="M25" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
